--- a/Assets/Excal/SceneInfo.xlsx
+++ b/Assets/Excal/SceneInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11160"/>
+    <workbookView windowWidth="22185" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -44,6 +44,12 @@
   </si>
   <si>
     <t>tips</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>towerHp</t>
   </si>
   <si>
     <t>SceneImg/GameScene1</t>
@@ -1026,8 +1032,7 @@
     <col min="3" max="3" width="8.875" customWidth="1"/>
     <col min="4" max="4" width="11.5" customWidth="1"/>
     <col min="5" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="6" width="8.375" customWidth="1"/>
-    <col min="7" max="7" width="6.375" customWidth="1"/>
+    <col min="6" max="7" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1046,65 +1051,81 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2">
+        <v>200</v>
+      </c>
+      <c r="G2" s="3">
+        <v>100</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2">
+        <v>200</v>
+      </c>
+      <c r="G3" s="3">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2">
+        <v>200</v>
+      </c>
+      <c r="G4" s="3">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
